--- a/docs/Mapping_casi_uso/morte/Morte_002.xlsx
+++ b/docs/Mapping_casi_uso/morte/Morte_002.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="192">
   <si>
     <t>Sezione</t>
   </si>
@@ -153,6 +153,12 @@
   </si>
   <si>
     <t>testoDataPresuntaMorte</t>
+  </si>
+  <si>
+    <t>Data rinvenimento cadavere</t>
+  </si>
+  <si>
+    <t>dataRinvenimentoCadavere</t>
   </si>
   <si>
     <t>Luogo</t>
@@ -640,7 +646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H128"/>
+  <dimension ref="A1:H129"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="26.12890625" customWidth="true" bestFit="true"/>
@@ -1229,19 +1235,19 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>10</v>
@@ -1252,16 +1258,16 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>68</v>
@@ -1275,16 +1281,16 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>70</v>
@@ -1298,7 +1304,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>71</v>
@@ -1307,7 +1313,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>72</v>
@@ -1321,16 +1327,16 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>74</v>
@@ -1344,16 +1350,16 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>76</v>
@@ -1367,7 +1373,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>77</v>
@@ -1376,7 +1382,7 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>78</v>
@@ -1390,16 +1396,16 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>80</v>
@@ -1413,7 +1419,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>81</v>
@@ -1422,7 +1428,7 @@
         <v>12</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>82</v>
@@ -1436,7 +1442,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>83</v>
@@ -1445,7 +1451,7 @@
         <v>12</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>84</v>
@@ -1459,16 +1465,16 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>86</v>
@@ -1482,7 +1488,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>87</v>
@@ -1491,7 +1497,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>88</v>
@@ -1505,7 +1511,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>89</v>
@@ -1514,7 +1520,7 @@
         <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>90</v>
@@ -1528,7 +1534,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>91</v>
@@ -1537,7 +1543,7 @@
         <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>92</v>
@@ -1551,7 +1557,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>93</v>
@@ -1560,7 +1566,7 @@
         <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>94</v>
@@ -1574,16 +1580,16 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>96</v>
@@ -1597,7 +1603,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>97</v>
@@ -1606,7 +1612,7 @@
         <v>12</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>98</v>
@@ -1620,16 +1626,16 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>100</v>
@@ -1643,7 +1649,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>101</v>
@@ -1652,7 +1658,7 @@
         <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>102</v>
@@ -1666,7 +1672,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>103</v>
@@ -1675,7 +1681,7 @@
         <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>104</v>
@@ -1689,7 +1695,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>105</v>
@@ -1698,7 +1704,7 @@
         <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>106</v>
@@ -1712,7 +1718,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>107</v>
@@ -1721,7 +1727,7 @@
         <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>108</v>
@@ -1735,7 +1741,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>109</v>
@@ -1744,7 +1750,7 @@
         <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>110</v>
@@ -1758,7 +1764,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>111</v>
@@ -1767,7 +1773,7 @@
         <v>9</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>112</v>
@@ -1781,7 +1787,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>113</v>
@@ -1790,7 +1796,7 @@
         <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>114</v>
@@ -1804,7 +1810,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>115</v>
@@ -1813,7 +1819,7 @@
         <v>9</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>116</v>
@@ -1827,7 +1833,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>117</v>
@@ -1836,7 +1842,7 @@
         <v>9</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>118</v>
@@ -1850,7 +1856,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>119</v>
@@ -1859,7 +1865,7 @@
         <v>9</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>120</v>
@@ -1873,7 +1879,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>121</v>
@@ -1882,7 +1888,7 @@
         <v>9</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>122</v>
@@ -1896,39 +1902,39 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="C55" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D55" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E55" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="E55" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="F55" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>125</v>
+        <v>18</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>68</v>
@@ -1937,35 +1943,35 @@
         <v>10</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>73</v>
@@ -1974,7 +1980,7 @@
         <v>9</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>74</v>
@@ -1983,12 +1989,12 @@
         <v>10</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>75</v>
@@ -1997,7 +2003,7 @@
         <v>9</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>76</v>
@@ -2006,12 +2012,12 @@
         <v>10</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>77</v>
@@ -2020,7 +2026,7 @@
         <v>9</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>78</v>
@@ -2029,12 +2035,12 @@
         <v>10</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>79</v>
@@ -2043,7 +2049,7 @@
         <v>9</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>80</v>
@@ -2052,21 +2058,21 @@
         <v>10</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>82</v>
@@ -2075,21 +2081,21 @@
         <v>10</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>84</v>
@@ -2098,21 +2104,21 @@
         <v>10</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>86</v>
@@ -2121,21 +2127,21 @@
         <v>10</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>88</v>
@@ -2144,21 +2150,21 @@
         <v>10</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>90</v>
@@ -2167,21 +2173,21 @@
         <v>10</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>92</v>
@@ -2190,21 +2196,21 @@
         <v>10</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>94</v>
@@ -2213,12 +2219,12 @@
         <v>10</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>95</v>
@@ -2227,7 +2233,7 @@
         <v>9</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>96</v>
@@ -2236,21 +2242,21 @@
         <v>10</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>132</v>
+        <v>97</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>98</v>
@@ -2259,67 +2265,67 @@
         <v>10</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>135</v>
+        <v>101</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>102</v>
@@ -2328,21 +2334,21 @@
         <v>10</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>104</v>
@@ -2351,21 +2357,21 @@
         <v>10</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>106</v>
@@ -2374,21 +2380,21 @@
         <v>10</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>108</v>
@@ -2397,21 +2403,21 @@
         <v>10</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>110</v>
@@ -2420,21 +2426,21 @@
         <v>10</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>112</v>
@@ -2443,21 +2449,21 @@
         <v>10</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>114</v>
@@ -2466,35 +2472,35 @@
         <v>10</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>144</v>
@@ -2503,7 +2509,7 @@
         <v>9</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>145</v>
@@ -2512,12 +2518,12 @@
         <v>10</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>146</v>
@@ -2526,7 +2532,7 @@
         <v>9</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>147</v>
@@ -2535,44 +2541,44 @@
         <v>10</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B83" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="B83" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="C83" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>66</v>
+        <v>149</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>68</v>
@@ -2581,35 +2587,35 @@
         <v>10</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>73</v>
@@ -2618,7 +2624,7 @@
         <v>9</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>74</v>
@@ -2627,12 +2633,12 @@
         <v>10</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>75</v>
@@ -2641,7 +2647,7 @@
         <v>9</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>76</v>
@@ -2650,12 +2656,12 @@
         <v>10</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>77</v>
@@ -2664,7 +2670,7 @@
         <v>9</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>78</v>
@@ -2673,12 +2679,12 @@
         <v>10</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>79</v>
@@ -2687,7 +2693,7 @@
         <v>9</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>80</v>
@@ -2696,21 +2702,21 @@
         <v>10</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>82</v>
@@ -2719,21 +2725,21 @@
         <v>10</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>84</v>
@@ -2742,21 +2748,21 @@
         <v>10</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>86</v>
@@ -2765,21 +2771,21 @@
         <v>10</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>88</v>
@@ -2788,21 +2794,21 @@
         <v>10</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>90</v>
@@ -2811,21 +2817,21 @@
         <v>10</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>92</v>
@@ -2834,21 +2840,21 @@
         <v>10</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>94</v>
@@ -2857,12 +2863,12 @@
         <v>10</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>95</v>
@@ -2871,7 +2877,7 @@
         <v>9</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>96</v>
@@ -2880,21 +2886,21 @@
         <v>10</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>132</v>
+        <v>97</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>98</v>
@@ -2903,67 +2909,67 @@
         <v>10</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>135</v>
+        <v>101</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>102</v>
@@ -2972,21 +2978,21 @@
         <v>10</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>104</v>
@@ -2995,21 +3001,21 @@
         <v>10</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>106</v>
@@ -3018,21 +3024,21 @@
         <v>10</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>108</v>
@@ -3041,21 +3047,21 @@
         <v>10</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>110</v>
@@ -3064,21 +3070,21 @@
         <v>10</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>112</v>
@@ -3087,21 +3093,21 @@
         <v>10</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>114</v>
@@ -3110,35 +3116,35 @@
         <v>10</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>144</v>
@@ -3147,7 +3153,7 @@
         <v>9</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>145</v>
@@ -3156,12 +3162,12 @@
         <v>10</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>146</v>
@@ -3170,7 +3176,7 @@
         <v>9</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>147</v>
@@ -3179,7 +3185,7 @@
         <v>10</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="111">
@@ -3187,27 +3193,27 @@
         <v>150</v>
       </c>
       <c r="B111" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G111" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D111" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E111" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="F111" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G111" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>153</v>
@@ -3216,7 +3222,7 @@
         <v>12</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>154</v>
@@ -3230,53 +3236,53 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B113" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B113" s="2" t="s">
+      <c r="C113" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E113" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C113" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E113" s="2" t="s">
-        <v>158</v>
-      </c>
       <c r="F113" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>159</v>
+        <v>18</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B114" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E114" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C114" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D114" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E114" s="2" t="s">
+      <c r="F114" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G114" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="F114" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G114" s="2" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>162</v>
@@ -3285,7 +3291,7 @@
         <v>9</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>163</v>
@@ -3294,12 +3300,12 @@
         <v>10</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>164</v>
@@ -3308,7 +3314,7 @@
         <v>9</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>165</v>
@@ -3317,12 +3323,12 @@
         <v>10</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>166</v>
@@ -3331,7 +3337,7 @@
         <v>9</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>167</v>
@@ -3340,12 +3346,12 @@
         <v>10</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>168</v>
@@ -3354,7 +3360,7 @@
         <v>9</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>169</v>
@@ -3363,12 +3369,12 @@
         <v>10</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>170</v>
@@ -3377,44 +3383,44 @@
         <v>9</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>17</v>
+        <v>171</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>172</v>
+        <v>17</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>173</v>
@@ -3423,44 +3429,44 @@
         <v>9</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>20</v>
+        <v>174</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>175</v>
+        <v>20</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>176</v>
@@ -3469,7 +3475,7 @@
         <v>9</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>177</v>
@@ -3478,12 +3484,12 @@
         <v>10</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>178</v>
@@ -3492,7 +3498,7 @@
         <v>9</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>179</v>
@@ -3501,12 +3507,12 @@
         <v>10</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>180</v>
@@ -3515,7 +3521,7 @@
         <v>9</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>181</v>
@@ -3524,44 +3530,44 @@
         <v>10</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B126" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B126" s="2" t="s">
+      <c r="C126" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E126" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C126" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="E126" s="2" t="s">
-        <v>185</v>
-      </c>
       <c r="F126" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>18</v>
+        <v>161</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B127" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D127" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D127" s="2" t="s">
-        <v>184</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>187</v>
@@ -3575,7 +3581,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>188</v>
@@ -3584,7 +3590,7 @@
         <v>9</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>189</v>
@@ -3593,6 +3599,29 @@
         <v>10</v>
       </c>
       <c r="G128" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G129" s="2" t="s">
         <v>18</v>
       </c>
     </row>
